--- a/Output/results_carbam_prots.xlsx
+++ b/Output/results_carbam_prots.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charliebrown/code/GitHub/carbamylation/Output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{360ACBA9-EBC5-C44B-BB48-70E0DCD8E444}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{82049D96-B5D2-8D4D-8022-77515EDA3995}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1220" yWindow="1000" windowWidth="19740" windowHeight="16440"/>
+    <workbookView xWindow="8260" yWindow="600" windowWidth="29800" windowHeight="16440"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
